--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A98FA7D-654F-4B5C-B998-407BD5415376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90398D30-4026-4C59-9BE4-510BB075FE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB75EA85-02DD-47F0-AA4A-55FDB50CE8D6}"/>
   </bookViews>
@@ -322,7 +322,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -374,12 +374,36 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -389,29 +413,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1466,80 +1469,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
     </row>
     <row r="2" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="28" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
     </row>
     <row r="3" spans="1:33" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="19"/>
@@ -1577,49 +1580,49 @@
       <c r="AG3" s="17"/>
     </row>
     <row r="4" spans="1:33" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="33"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
     </row>
     <row r="5" spans="1:33" s="8" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="30"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="9">
         <v>1</v>
       </c>
@@ -1990,37 +1993,37 @@
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="26"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="26"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="26"/>
-      <c r="AB13" s="26"/>
-      <c r="AC13" s="26"/>
-      <c r="AD13" s="26"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
+      <c r="AF13" s="21"/>
+      <c r="AG13" s="21"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="5"/>
@@ -2058,37 +2061,37 @@
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="5"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="30"/>
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
@@ -2129,69 +2132,100 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:33" ht="224.25" customHeight="1"/>
+    <row r="18" spans="2:33" ht="224.25" customHeight="1">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="34"/>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="34"/>
+      <c r="AC18" s="34"/>
+      <c r="AD18" s="34"/>
+      <c r="AE18" s="34"/>
+      <c r="AF18" s="34"/>
+      <c r="AG18" s="34"/>
+    </row>
     <row r="19" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="20" spans="2:33" ht="23.25" customHeight="1">
       <c r="AB20" s="4"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
     </row>
     <row r="21" spans="2:33" ht="23.25" customHeight="1">
-      <c r="AC21" s="25" t="s">
+      <c r="AC21" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="AD21" s="25"/>
-      <c r="AE21" s="25"/>
-      <c r="AF21" s="25"/>
-      <c r="AG21" s="25"/>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="33"/>
     </row>
     <row r="22" spans="2:33" ht="7.5" customHeight="1">
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="2:33" ht="14.25" customHeight="1">
       <c r="C23" s="2"/>
-      <c r="AC23" s="23" t="s">
+      <c r="AC23" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="AD23" s="23"/>
-      <c r="AE23" s="23"/>
-      <c r="AF23" s="23"/>
-      <c r="AG23" s="23"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
+  <mergeCells count="72">
+    <mergeCell ref="AC23:AG23"/>
+    <mergeCell ref="AD15:AD16"/>
+    <mergeCell ref="AE15:AE16"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="AG15:AG16"/>
+    <mergeCell ref="AC20:AG20"/>
+    <mergeCell ref="AC21:AG21"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="B18:AG18"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="J15:J16"/>
@@ -2208,32 +2242,35 @@
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="U15:U16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="AC23:AG23"/>
-    <mergeCell ref="AD15:AD16"/>
-    <mergeCell ref="AE15:AE16"/>
-    <mergeCell ref="AF15:AF16"/>
-    <mergeCell ref="AG15:AG16"/>
-    <mergeCell ref="AC20:AG20"/>
-    <mergeCell ref="AC21:AG21"/>
-    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -314,7 +314,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -422,6 +422,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1732,9 +1735,17 @@
           <t>ตรวจเช็คระบบน้ำหม้อน้ำให้อยู่ในระดับ Hight</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F6" s="9" t="inlineStr"/>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
@@ -1773,7 +1784,11 @@
           <t>ตรวจเช็คน้ำมันเครื่องยนต์ต้องอยู่ไม่เกินขีดที่3ของตัวเช็ค</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="inlineStr"/>
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr"/>
@@ -1814,7 +1829,11 @@
           <t>ตรวจเช็คไส้กรองและเป่าลมทำความสะอาด</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="inlineStr"/>
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr"/>
@@ -1855,9 +1874,17 @@
           <t>ตรวจเช็คการรั่วซึมของน้ำมันไฮดรอริก</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F9" s="9" t="inlineStr"/>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
@@ -1896,9 +1923,17 @@
           <t>ตรวจเช็คระบบเบรคและน้ำมันเบรค</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F10" s="9" t="inlineStr"/>
       <c r="G10" s="9" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr"/>
@@ -1937,9 +1972,17 @@
           <t>ตรวจเช็คไฟส่องสว่างและไฟเลี้ยว</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F11" s="9" t="inlineStr"/>
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
@@ -2013,9 +2056,17 @@
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="40" t="inlineStr"/>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="D13" s="40" t="inlineStr"/>
-      <c r="E13" s="40" t="inlineStr"/>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="F13" s="40" t="inlineStr"/>
       <c r="G13" s="40" t="inlineStr"/>
       <c r="H13" s="40" t="inlineStr"/>
@@ -2155,7 +2206,11 @@
       </c>
     </row>
     <row r="18" ht="224.25" customHeight="1">
-      <c r="B18" s="41" t="inlineStr"/>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>[วันที่ 1]: หน้าปัดมองไม่ชัด,  [วันที่ 3]: หน้าปัดมองไม่ชัด</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1"/>
     <row r="20" ht="23.25" customHeight="1">

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -1735,17 +1735,9 @@
           <t>ตรวจเช็คระบบน้ำหม้อน้ำให้อยู่ในระดับ Hight</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C6" s="9" t="inlineStr"/>
       <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr"/>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr"/>
@@ -1784,11 +1776,7 @@
           <t>ตรวจเช็คน้ำมันเครื่องยนต์ต้องอยู่ไม่เกินขีดที่3ของตัวเช็ค</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="9" t="inlineStr"/>
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr"/>
@@ -1829,11 +1817,7 @@
           <t>ตรวจเช็คไส้กรองและเป่าลมทำความสะอาด</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C8" s="9" t="inlineStr"/>
       <c r="D8" s="9" t="inlineStr"/>
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr"/>
@@ -1874,17 +1858,9 @@
           <t>ตรวจเช็คการรั่วซึมของน้ำมันไฮดรอริก</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C9" s="9" t="inlineStr"/>
       <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr"/>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
@@ -1923,17 +1899,9 @@
           <t>ตรวจเช็คระบบเบรคและน้ำมันเบรค</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C10" s="9" t="inlineStr"/>
       <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr"/>
       <c r="G10" s="9" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr"/>
@@ -1972,17 +1940,9 @@
           <t>ตรวจเช็คไฟส่องสว่างและไฟเลี้ยว</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr"/>
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
@@ -2056,17 +2016,9 @@
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>คะนอง บัวจันทร์</t>
-        </is>
-      </c>
+      <c r="C13" s="43" t="inlineStr"/>
       <c r="D13" s="40" t="inlineStr"/>
-      <c r="E13" s="43" t="inlineStr">
-        <is>
-          <t>คะนอง บัวจันทร์</t>
-        </is>
-      </c>
+      <c r="E13" s="43" t="inlineStr"/>
       <c r="F13" s="40" t="inlineStr"/>
       <c r="G13" s="40" t="inlineStr"/>
       <c r="H13" s="40" t="inlineStr"/>
@@ -2206,11 +2158,7 @@
       </c>
     </row>
     <row r="18" ht="224.25" customHeight="1">
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>[วันที่ 1]: หน้าปัดมองไม่ชัด,  [วันที่ 3]: หน้าปัดมองไม่ชัด</t>
-        </is>
-      </c>
+      <c r="B18" s="41" t="inlineStr"/>
     </row>
     <row r="19" ht="23.25" customHeight="1"/>
     <row r="20" ht="23.25" customHeight="1">

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -1740,7 +1740,11 @@
       <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr"/>
       <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
@@ -1781,7 +1785,11 @@
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="9" t="inlineStr"/>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1822,7 +1830,11 @@
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr"/>
       <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr"/>
@@ -1863,7 +1875,11 @@
       <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr"/>
       <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1904,7 +1920,11 @@
       <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr"/>
       <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="9" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr"/>
@@ -1945,7 +1965,11 @@
       <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr"/>
       <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="9" t="inlineStr"/>
       <c r="K11" s="9" t="inlineStr"/>
@@ -1986,7 +2010,11 @@
       <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr"/>
       <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr"/>
@@ -2021,7 +2049,11 @@
       <c r="E13" s="43" t="inlineStr"/>
       <c r="F13" s="40" t="inlineStr"/>
       <c r="G13" s="40" t="inlineStr"/>
-      <c r="H13" s="40" t="inlineStr"/>
+      <c r="H13" s="43" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="I13" s="40" t="inlineStr"/>
       <c r="J13" s="40" t="inlineStr"/>
       <c r="K13" s="40" t="inlineStr"/>
@@ -2158,7 +2190,11 @@
       </c>
     </row>
     <row r="18" ht="224.25" customHeight="1">
-      <c r="B18" s="41" t="inlineStr"/>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1"/>
     <row r="20" ht="23.25" customHeight="1">

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -1745,7 +1745,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr"/>
@@ -1790,7 +1794,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr"/>
@@ -1835,7 +1843,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr"/>
@@ -1880,7 +1892,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr"/>
@@ -1925,7 +1941,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="9" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr"/>
@@ -1970,7 +1990,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr"/>
       <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr"/>
@@ -2015,7 +2039,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr"/>
@@ -2054,7 +2082,11 @@
           <t>คะนอง บัวจันทร์</t>
         </is>
       </c>
-      <c r="I13" s="40" t="inlineStr"/>
+      <c r="I13" s="43" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="J13" s="40" t="inlineStr"/>
       <c r="K13" s="40" t="inlineStr"/>
       <c r="L13" s="40" t="inlineStr"/>
@@ -2192,7 +2224,7 @@
     <row r="18" ht="224.25" customHeight="1">
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด</t>
+          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 2: หน้าปัดมองไม่ชัด</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -2224,7 +2224,7 @@
     <row r="18" ht="224.25" customHeight="1">
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 2: หน้าปัดมองไม่ชัด</t>
+          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 2: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 5: หน้าปัดมองไม่ชัด</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -1750,7 +1750,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr"/>
       <c r="M6" s="9" t="inlineStr"/>
@@ -1799,7 +1803,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr"/>
       <c r="M7" s="9" t="inlineStr"/>
@@ -1848,7 +1856,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr"/>
       <c r="M8" s="9" t="inlineStr"/>
@@ -1897,7 +1909,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr"/>
       <c r="M9" s="9" t="inlineStr"/>
@@ -1946,7 +1962,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr"/>
       <c r="M10" s="9" t="inlineStr"/>
@@ -1995,7 +2015,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr"/>
       <c r="M11" s="9" t="inlineStr"/>
@@ -2044,7 +2068,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="9" t="inlineStr"/>
@@ -2087,7 +2115,11 @@
           <t>คะนอง บัวจันทร์</t>
         </is>
       </c>
-      <c r="J13" s="40" t="inlineStr"/>
+      <c r="J13" s="43" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="K13" s="40" t="inlineStr"/>
       <c r="L13" s="40" t="inlineStr"/>
       <c r="M13" s="40" t="inlineStr"/>
@@ -2224,7 +2256,7 @@
     <row r="18" ht="224.25" customHeight="1">
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 2: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 5: หน้าปัดมองไม่ชัด</t>
+          <t>[วันที่ 6]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 2: หน้าปัดมองไม่ชัด,  [วันที่ 7]: ข้อ 5: หน้าปัดมองไม่ชัด,  [วันที่ 8]: ข้อ 2: หน้าปัดมองไม่ชัด, ข้อ 5: หน้าปัดมองไม่ชัด</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_FORKLIFT-01.xlsx
+++ b/FM-MN-07_FORKLIFT-01.xlsx
@@ -1756,7 +1756,11 @@
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="9" t="inlineStr"/>
       <c r="N6" s="9" t="inlineStr"/>
       <c r="O6" s="9" t="inlineStr"/>
@@ -1809,7 +1813,11 @@
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="9" t="inlineStr"/>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="9" t="inlineStr"/>
@@ -1862,7 +1870,11 @@
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="9" t="inlineStr"/>
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="9" t="inlineStr"/>
@@ -1915,7 +1927,11 @@
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="9" t="inlineStr"/>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="9" t="inlineStr"/>
@@ -1968,7 +1984,11 @@
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="9" t="inlineStr"/>
       <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="9" t="inlineStr"/>
@@ -2021,7 +2041,11 @@
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="9" t="inlineStr"/>
       <c r="N11" s="9" t="inlineStr"/>
       <c r="O11" s="9" t="inlineStr"/>
@@ -2074,7 +2098,11 @@
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="9" t="inlineStr"/>
       <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="9" t="inlineStr"/>
@@ -2121,7 +2149,11 @@
         </is>
       </c>
       <c r="K13" s="40" t="inlineStr"/>
-      <c r="L13" s="40" t="inlineStr"/>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>คะนอง บัวจันทร์</t>
+        </is>
+      </c>
       <c r="M13" s="40" t="inlineStr"/>
       <c r="N13" s="40" t="inlineStr"/>
       <c r="O13" s="40" t="inlineStr"/>
